--- a/NXT.L.xlsx
+++ b/NXT.L.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37B8C5A9-AC0C-4B76-B137-458888AD29AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB2C4AE5-A903-4177-A8C2-4760E7E2F9C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="225" yWindow="390" windowWidth="38175" windowHeight="15240" xr2:uid="{0F543347-D4D0-4782-A0BE-24D35C709E73}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" activeTab="1" xr2:uid="{0F543347-D4D0-4782-A0BE-24D35C709E73}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -71,7 +71,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="59">
   <si>
     <t>Next PLC</t>
   </si>
@@ -238,13 +238,16 @@
     <t>Levis, Babour, Adidas, Nike, Boss, The North Face etc.</t>
   </si>
   <si>
-    <t>Q225</t>
-  </si>
-  <si>
     <t>H122</t>
   </si>
   <si>
     <t>H222</t>
+  </si>
+  <si>
+    <t>FY26</t>
+  </si>
+  <si>
+    <t>Q425</t>
   </si>
 </sst>
 </file>
@@ -257,13 +260,19 @@
     <numFmt numFmtId="166" formatCode="#,##0.00;\(#,##0.00\)"/>
     <numFmt numFmtId="167" formatCode="#,##0;\(#,##0\)"/>
   </numFmts>
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -471,40 +480,44 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="3" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
@@ -863,7 +876,7 @@
         <v>2</v>
       </c>
       <c r="I2" s="3">
-        <v>127.35</v>
+        <v>156</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.2">
@@ -871,10 +884,10 @@
         <v>3</v>
       </c>
       <c r="I3" s="22">
-        <v>117.1</v>
-      </c>
-      <c r="J3" s="25" t="s">
-        <v>55</v>
+        <v>116.9</v>
+      </c>
+      <c r="J3" s="26" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.2">
@@ -886,7 +899,7 @@
       </c>
       <c r="I4" s="3">
         <f>+I2*I3</f>
-        <v>14912.684999999999</v>
+        <v>18236.400000000001</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.2">
@@ -896,11 +909,11 @@
       <c r="H5" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I5" s="3">
-        <v>441.1</v>
-      </c>
-      <c r="J5" s="25" t="s">
-        <v>55</v>
+      <c r="I5" s="27">
+        <v>96.2</v>
+      </c>
+      <c r="J5" s="26" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.2">
@@ -908,11 +921,11 @@
         <v>6</v>
       </c>
       <c r="I6" s="3">
-        <f>15.1+712.1+54.1</f>
-        <v>781.30000000000007</v>
-      </c>
-      <c r="J6" s="25" t="s">
-        <v>55</v>
+        <f>96+112.9+600</f>
+        <v>808.9</v>
+      </c>
+      <c r="J6" s="26" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
@@ -929,7 +942,7 @@
       </c>
       <c r="I7" s="3">
         <f>+I4-I5+I6</f>
-        <v>15252.884999999998</v>
+        <v>18949.100000000002</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.2">
@@ -1015,10 +1028,10 @@
     </row>
     <row r="2" spans="1:47" x14ac:dyDescent="0.2">
       <c r="C2" s="25" t="s">
+        <v>55</v>
+      </c>
+      <c r="D2" s="25" t="s">
         <v>56</v>
-      </c>
-      <c r="D2" s="25" t="s">
-        <v>57</v>
       </c>
       <c r="E2" s="25" t="s">
         <v>11</v>
@@ -1062,6 +1075,9 @@
       </c>
       <c r="S2" s="4" t="s">
         <v>22</v>
+      </c>
+      <c r="T2" s="26" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="3" spans="1:47" x14ac:dyDescent="0.2">
@@ -1081,7 +1097,9 @@
       <c r="I3" s="21">
         <v>457</v>
       </c>
-      <c r="J3" s="21"/>
+      <c r="J3" s="21">
+        <v>458</v>
+      </c>
       <c r="K3" s="21"/>
       <c r="L3" s="21"/>
       <c r="M3" s="21"/>
@@ -1089,8 +1107,12 @@
       <c r="O3" s="21"/>
       <c r="P3" s="21"/>
       <c r="Q3" s="21"/>
-      <c r="R3" s="21"/>
-      <c r="S3" s="21"/>
+      <c r="R3" s="21">
+        <v>457</v>
+      </c>
+      <c r="S3" s="21">
+        <v>458</v>
+      </c>
       <c r="T3" s="21"/>
       <c r="U3" s="21"/>
       <c r="V3" s="21"/>
@@ -1137,7 +1159,9 @@
       <c r="I4" s="21">
         <v>8078</v>
       </c>
-      <c r="J4" s="21"/>
+      <c r="J4" s="21">
+        <v>8113</v>
+      </c>
       <c r="K4" s="21"/>
       <c r="L4" s="21"/>
       <c r="M4" s="21"/>
@@ -1145,8 +1169,12 @@
       <c r="O4" s="21"/>
       <c r="P4" s="21"/>
       <c r="Q4" s="21"/>
-      <c r="R4" s="21"/>
-      <c r="S4" s="21"/>
+      <c r="R4" s="21">
+        <v>8078</v>
+      </c>
+      <c r="S4" s="21">
+        <v>8113</v>
+      </c>
       <c r="T4" s="21"/>
       <c r="U4" s="21"/>
       <c r="V4" s="21"/>
@@ -1229,7 +1257,10 @@
         <f>1156.1+591.8</f>
         <v>1747.8999999999999</v>
       </c>
-      <c r="J6" s="22"/>
+      <c r="J6" s="22">
+        <f>+R6-I6</f>
+        <v>1731.1000000000001</v>
+      </c>
       <c r="K6" s="22"/>
       <c r="L6" s="22"/>
       <c r="M6" s="22"/>
@@ -1237,8 +1268,14 @@
       <c r="O6" s="22"/>
       <c r="P6" s="22"/>
       <c r="Q6" s="22"/>
-      <c r="R6" s="22"/>
-      <c r="S6" s="22"/>
+      <c r="R6" s="22">
+        <f>2549+930</f>
+        <v>3479</v>
+      </c>
+      <c r="S6" s="22">
+        <f>2800+1297</f>
+        <v>4097</v>
+      </c>
       <c r="T6" s="22"/>
       <c r="U6" s="22"/>
       <c r="V6" s="22"/>
@@ -1273,7 +1310,10 @@
       <c r="I7" s="22">
         <v>878.4</v>
       </c>
-      <c r="J7" s="22"/>
+      <c r="J7" s="22">
+        <f t="shared" ref="J7:J25" si="0">+R7-I7</f>
+        <v>970.6</v>
+      </c>
       <c r="K7" s="22"/>
       <c r="L7" s="22"/>
       <c r="M7" s="22"/>
@@ -1281,8 +1321,12 @@
       <c r="O7" s="22"/>
       <c r="P7" s="22"/>
       <c r="Q7" s="22"/>
-      <c r="R7" s="22"/>
-      <c r="S7" s="22"/>
+      <c r="R7" s="22">
+        <v>1849</v>
+      </c>
+      <c r="S7" s="22">
+        <v>1893</v>
+      </c>
       <c r="T7" s="22"/>
       <c r="U7" s="22"/>
       <c r="V7" s="22"/>
@@ -1317,7 +1361,10 @@
       <c r="I8" s="22">
         <v>151.1</v>
       </c>
-      <c r="J8" s="22"/>
+      <c r="J8" s="22">
+        <f t="shared" si="0"/>
+        <v>148.9</v>
+      </c>
       <c r="K8" s="22"/>
       <c r="L8" s="22"/>
       <c r="M8" s="22"/>
@@ -1325,8 +1372,12 @@
       <c r="O8" s="22"/>
       <c r="P8" s="22"/>
       <c r="Q8" s="22"/>
-      <c r="R8" s="22"/>
-      <c r="S8" s="22"/>
+      <c r="R8" s="22">
+        <v>300</v>
+      </c>
+      <c r="S8" s="22">
+        <v>301</v>
+      </c>
       <c r="T8" s="22"/>
       <c r="U8" s="22"/>
       <c r="V8" s="22"/>
@@ -1364,7 +1415,10 @@
         <f>318.9+48.2</f>
         <v>367.09999999999997</v>
       </c>
-      <c r="J9" s="22"/>
+      <c r="J9" s="22">
+        <f t="shared" si="0"/>
+        <v>-195.09999999999997</v>
+      </c>
       <c r="K9" s="22"/>
       <c r="L9" s="22"/>
       <c r="M9" s="22"/>
@@ -1372,8 +1426,14 @@
       <c r="O9" s="22"/>
       <c r="P9" s="22"/>
       <c r="Q9" s="22"/>
-      <c r="R9" s="22"/>
-      <c r="S9" s="22"/>
+      <c r="R9" s="22">
+        <f>67+105</f>
+        <v>172</v>
+      </c>
+      <c r="S9" s="22">
+        <f>78+104</f>
+        <v>182</v>
+      </c>
       <c r="T9" s="22"/>
       <c r="U9" s="22"/>
       <c r="V9" s="22"/>
@@ -1408,7 +1468,10 @@
       <c r="I10" s="23">
         <v>3144.5</v>
       </c>
-      <c r="J10" s="23"/>
+      <c r="J10" s="23">
+        <f t="shared" si="0"/>
+        <v>2973.6000000000004</v>
+      </c>
       <c r="K10" s="23"/>
       <c r="L10" s="23"/>
       <c r="M10" s="23"/>
@@ -1416,9 +1479,13 @@
       <c r="O10" s="23"/>
       <c r="P10" s="23"/>
       <c r="Q10" s="23"/>
-      <c r="R10" s="23"/>
-      <c r="S10" s="23"/>
-      <c r="T10" s="22"/>
+      <c r="R10" s="23">
+        <v>6118.1</v>
+      </c>
+      <c r="S10" s="23">
+        <v>6901.3</v>
+      </c>
+      <c r="T10" s="23"/>
       <c r="U10" s="22"/>
       <c r="V10" s="22"/>
       <c r="W10" s="22"/>
@@ -1452,7 +1519,10 @@
       <c r="I11" s="22">
         <v>1767.8</v>
       </c>
-      <c r="J11" s="22"/>
+      <c r="J11" s="22">
+        <f t="shared" si="0"/>
+        <v>1688.7</v>
+      </c>
       <c r="K11" s="22"/>
       <c r="L11" s="22"/>
       <c r="M11" s="22"/>
@@ -1460,8 +1530,12 @@
       <c r="O11" s="22"/>
       <c r="P11" s="22"/>
       <c r="Q11" s="22"/>
-      <c r="R11" s="22"/>
-      <c r="S11" s="22"/>
+      <c r="R11" s="22">
+        <v>3456.5</v>
+      </c>
+      <c r="S11" s="22">
+        <v>3847.5</v>
+      </c>
       <c r="T11" s="22"/>
       <c r="U11" s="22"/>
       <c r="V11" s="22"/>
@@ -1496,7 +1570,10 @@
       <c r="I12" s="22">
         <v>1.7</v>
       </c>
-      <c r="J12" s="22"/>
+      <c r="J12" s="22">
+        <f t="shared" si="0"/>
+        <v>17.7</v>
+      </c>
       <c r="K12" s="22"/>
       <c r="L12" s="22"/>
       <c r="M12" s="22"/>
@@ -1504,8 +1581,12 @@
       <c r="O12" s="22"/>
       <c r="P12" s="22"/>
       <c r="Q12" s="22"/>
-      <c r="R12" s="22"/>
-      <c r="S12" s="22"/>
+      <c r="R12" s="22">
+        <v>19.399999999999999</v>
+      </c>
+      <c r="S12" s="22">
+        <v>7.1</v>
+      </c>
       <c r="T12" s="22"/>
       <c r="U12" s="22"/>
       <c r="V12" s="22"/>
@@ -1528,11 +1609,11 @@
         <v>29</v>
       </c>
       <c r="C13" s="22">
-        <f t="shared" ref="C13:F13" si="0">+C10-C11-C12</f>
+        <f t="shared" ref="C13:F13" si="1">+C10-C11-C12</f>
         <v>0</v>
       </c>
       <c r="D13" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="E13" s="22">
@@ -1540,7 +1621,7 @@
         <v>1099.0999999999999</v>
       </c>
       <c r="F13" s="22">
-        <f t="shared" si="0"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="G13" s="22">
@@ -1548,23 +1629,50 @@
         <v>1221.3999999999999</v>
       </c>
       <c r="H13" s="22">
-        <f t="shared" ref="H13:I13" si="1">+H10-H11-H12</f>
+        <f t="shared" ref="H13:J13" si="2">+H10-H11-H12</f>
         <v>0</v>
       </c>
       <c r="I13" s="22">
-        <f t="shared" si="1"/>
+        <f t="shared" si="2"/>
         <v>1375</v>
       </c>
-      <c r="J13" s="22"/>
+      <c r="J13" s="22">
+        <f t="shared" si="2"/>
+        <v>1267.2000000000003</v>
+      </c>
       <c r="K13" s="22"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="22"/>
-      <c r="O13" s="22"/>
-      <c r="P13" s="22"/>
-      <c r="Q13" s="22"/>
-      <c r="R13" s="22"/>
-      <c r="S13" s="22"/>
+      <c r="L13" s="22">
+        <f t="shared" ref="L13:T13" si="3">+L10-L11-L12</f>
+        <v>0</v>
+      </c>
+      <c r="M13" s="22">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="N13" s="22">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="O13" s="22">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="P13" s="22">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="Q13" s="22">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="R13" s="22">
+        <f t="shared" ref="R13:S13" si="4">+R10-R11-R12</f>
+        <v>2642.2000000000003</v>
+      </c>
+      <c r="S13" s="22">
+        <f t="shared" si="4"/>
+        <v>3046.7000000000003</v>
+      </c>
       <c r="T13" s="22"/>
       <c r="U13" s="22"/>
       <c r="V13" s="22"/>
@@ -1599,7 +1707,10 @@
       <c r="I14" s="22">
         <v>482.7</v>
       </c>
-      <c r="J14" s="22"/>
+      <c r="J14" s="22">
+        <f t="shared" si="0"/>
+        <v>396.09999999999997</v>
+      </c>
       <c r="K14" s="22"/>
       <c r="L14" s="22"/>
       <c r="M14" s="22"/>
@@ -1607,8 +1718,12 @@
       <c r="O14" s="22"/>
       <c r="P14" s="22"/>
       <c r="Q14" s="22"/>
-      <c r="R14" s="22"/>
-      <c r="S14" s="22"/>
+      <c r="R14" s="22">
+        <v>878.8</v>
+      </c>
+      <c r="S14" s="22">
+        <v>1027.0999999999999</v>
+      </c>
       <c r="T14" s="22"/>
       <c r="U14" s="22"/>
       <c r="V14" s="22"/>
@@ -1643,7 +1758,10 @@
       <c r="I15" s="22">
         <v>345.2</v>
       </c>
-      <c r="J15" s="22"/>
+      <c r="J15" s="22">
+        <f t="shared" si="0"/>
+        <v>325.40000000000003</v>
+      </c>
       <c r="K15" s="22"/>
       <c r="L15" s="22"/>
       <c r="M15" s="22"/>
@@ -1651,8 +1769,12 @@
       <c r="O15" s="22"/>
       <c r="P15" s="22"/>
       <c r="Q15" s="22"/>
-      <c r="R15" s="22"/>
-      <c r="S15" s="22"/>
+      <c r="R15" s="22">
+        <v>670.6</v>
+      </c>
+      <c r="S15" s="22">
+        <v>742.4</v>
+      </c>
       <c r="T15" s="22"/>
       <c r="U15" s="22"/>
       <c r="V15" s="22"/>
@@ -1687,7 +1809,10 @@
       <c r="I16" s="22">
         <v>2.4</v>
       </c>
-      <c r="J16" s="22"/>
+      <c r="J16" s="22">
+        <f t="shared" si="0"/>
+        <v>1</v>
+      </c>
       <c r="K16" s="22"/>
       <c r="L16" s="22"/>
       <c r="M16" s="22"/>
@@ -1695,8 +1820,12 @@
       <c r="O16" s="22"/>
       <c r="P16" s="22"/>
       <c r="Q16" s="22"/>
-      <c r="R16" s="22"/>
-      <c r="S16" s="22"/>
+      <c r="R16" s="22">
+        <v>3.4</v>
+      </c>
+      <c r="S16" s="22">
+        <v>-3.4</v>
+      </c>
       <c r="T16" s="22"/>
       <c r="U16" s="22"/>
       <c r="V16" s="22"/>
@@ -1731,7 +1860,10 @@
       <c r="I17" s="22">
         <v>3.1</v>
       </c>
-      <c r="J17" s="22"/>
+      <c r="J17" s="22">
+        <f t="shared" si="0"/>
+        <v>-9.4</v>
+      </c>
       <c r="K17" s="22"/>
       <c r="L17" s="22"/>
       <c r="M17" s="22"/>
@@ -1739,8 +1871,13 @@
       <c r="O17" s="22"/>
       <c r="P17" s="22"/>
       <c r="Q17" s="22"/>
-      <c r="R17" s="22"/>
-      <c r="S17" s="22"/>
+      <c r="R17" s="22">
+        <f>6.7-13</f>
+        <v>-6.3</v>
+      </c>
+      <c r="S17" s="22">
+        <v>7.9</v>
+      </c>
       <c r="T17" s="22"/>
       <c r="U17" s="22"/>
       <c r="V17" s="22"/>
@@ -1775,7 +1912,10 @@
       <c r="I18" s="22">
         <v>0</v>
       </c>
-      <c r="J18" s="22"/>
+      <c r="J18" s="22">
+        <f t="shared" si="0"/>
+        <v>-14.5</v>
+      </c>
       <c r="K18" s="22"/>
       <c r="L18" s="22"/>
       <c r="M18" s="22"/>
@@ -1783,8 +1923,12 @@
       <c r="O18" s="22"/>
       <c r="P18" s="22"/>
       <c r="Q18" s="22"/>
-      <c r="R18" s="22"/>
-      <c r="S18" s="22"/>
+      <c r="R18" s="22">
+        <v>-14.5</v>
+      </c>
+      <c r="S18" s="22">
+        <v>-2.9</v>
+      </c>
       <c r="T18" s="22"/>
       <c r="U18" s="22"/>
       <c r="V18" s="22"/>
@@ -1807,19 +1951,19 @@
         <v>35</v>
       </c>
       <c r="C19" s="22">
-        <f t="shared" ref="C19:F19" si="2">+C13-SUM(C14:C15)+C16+C17+C18</f>
+        <f t="shared" ref="C19:F19" si="5">+C13-SUM(C14:C15)+C16+C17+C18</f>
         <v>0</v>
       </c>
       <c r="D19" s="22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E19" s="22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>452.49999999999989</v>
       </c>
       <c r="F19" s="22">
-        <f t="shared" si="2"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="G19" s="22">
@@ -1827,23 +1971,50 @@
         <v>475.69999999999976</v>
       </c>
       <c r="H19" s="22">
-        <f t="shared" ref="H19:I19" si="3">+H13-SUM(H14:H15)+H16+H17+H18</f>
+        <f t="shared" ref="H19:J19" si="6">+H13-SUM(H14:H15)+H16+H17+H18</f>
         <v>0</v>
       </c>
       <c r="I19" s="22">
-        <f t="shared" si="3"/>
+        <f t="shared" si="6"/>
         <v>552.6</v>
       </c>
-      <c r="J19" s="22"/>
+      <c r="J19" s="22">
+        <f t="shared" si="6"/>
+        <v>522.8000000000003</v>
+      </c>
       <c r="K19" s="22"/>
-      <c r="L19" s="22"/>
-      <c r="M19" s="22"/>
-      <c r="N19" s="22"/>
-      <c r="O19" s="22"/>
-      <c r="P19" s="22"/>
-      <c r="Q19" s="22"/>
-      <c r="R19" s="22"/>
-      <c r="S19" s="22"/>
+      <c r="L19" s="22">
+        <f t="shared" ref="L19:T19" si="7">+L13-SUM(L14:L15)+L16+L17+L18</f>
+        <v>0</v>
+      </c>
+      <c r="M19" s="22">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="N19" s="22">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="O19" s="22">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="P19" s="22">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="Q19" s="22">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="R19" s="22">
+        <f t="shared" ref="R19:S19" si="8">+R13-SUM(R14:R15)+R16+R17+R18</f>
+        <v>1075.4000000000003</v>
+      </c>
+      <c r="S19" s="22">
+        <f t="shared" si="8"/>
+        <v>1278.8000000000002</v>
+      </c>
       <c r="T19" s="22"/>
       <c r="U19" s="22"/>
       <c r="V19" s="22"/>
@@ -1878,7 +2049,10 @@
       <c r="I20" s="22">
         <v>5.4</v>
       </c>
-      <c r="J20" s="22"/>
+      <c r="J20" s="22">
+        <f t="shared" si="0"/>
+        <v>2.7999999999999989</v>
+      </c>
       <c r="K20" s="22"/>
       <c r="L20" s="22"/>
       <c r="M20" s="22"/>
@@ -1886,8 +2060,12 @@
       <c r="O20" s="22"/>
       <c r="P20" s="22"/>
       <c r="Q20" s="22"/>
-      <c r="R20" s="22"/>
-      <c r="S20" s="22"/>
+      <c r="R20" s="22">
+        <v>8.1999999999999993</v>
+      </c>
+      <c r="S20" s="22">
+        <v>11</v>
+      </c>
       <c r="T20" s="22"/>
       <c r="U20" s="22"/>
       <c r="V20" s="22"/>
@@ -1922,7 +2100,10 @@
       <c r="I21" s="22">
         <v>49</v>
       </c>
-      <c r="J21" s="22"/>
+      <c r="J21" s="22">
+        <f t="shared" si="0"/>
+        <v>47.599999999999994</v>
+      </c>
       <c r="K21" s="22"/>
       <c r="L21" s="22"/>
       <c r="M21" s="22"/>
@@ -1930,8 +2111,12 @@
       <c r="O21" s="22"/>
       <c r="P21" s="22"/>
       <c r="Q21" s="22"/>
-      <c r="R21" s="22"/>
-      <c r="S21" s="22"/>
+      <c r="R21" s="22">
+        <v>96.6</v>
+      </c>
+      <c r="S21" s="22">
+        <v>97.2</v>
+      </c>
       <c r="T21" s="22"/>
       <c r="U21" s="22"/>
       <c r="V21" s="22"/>
@@ -1954,19 +2139,19 @@
         <v>38</v>
       </c>
       <c r="C22" s="22">
-        <f t="shared" ref="C22:F22" si="4">+C19+C20-C21</f>
+        <f t="shared" ref="C22:F22" si="9">+C19+C20-C21</f>
         <v>0</v>
       </c>
       <c r="D22" s="22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="E22" s="22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>415.69999999999993</v>
       </c>
       <c r="F22" s="22">
-        <f t="shared" si="4"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="G22" s="22">
@@ -1974,23 +2159,50 @@
         <v>432.0999999999998</v>
       </c>
       <c r="H22" s="22">
-        <f t="shared" ref="H22:I22" si="5">+H19+H20-H21</f>
+        <f t="shared" ref="H22:J22" si="10">+H19+H20-H21</f>
         <v>0</v>
       </c>
       <c r="I22" s="22">
-        <f t="shared" si="5"/>
+        <f t="shared" si="10"/>
         <v>509</v>
       </c>
-      <c r="J22" s="22"/>
+      <c r="J22" s="22">
+        <f t="shared" si="10"/>
+        <v>478.00000000000023</v>
+      </c>
       <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
-      <c r="M22" s="22"/>
-      <c r="N22" s="22"/>
-      <c r="O22" s="22"/>
-      <c r="P22" s="22"/>
-      <c r="Q22" s="22"/>
-      <c r="R22" s="22"/>
-      <c r="S22" s="22"/>
+      <c r="L22" s="22">
+        <f t="shared" ref="L22:T22" si="11">+L19+L20-L21</f>
+        <v>0</v>
+      </c>
+      <c r="M22" s="22">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="N22" s="22">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="O22" s="22">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="P22" s="22">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="Q22" s="22">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="R22" s="22">
+        <f t="shared" ref="R22:S22" si="12">+R19+R20-R21</f>
+        <v>987.00000000000034</v>
+      </c>
+      <c r="S22" s="22">
+        <f t="shared" si="12"/>
+        <v>1192.6000000000001</v>
+      </c>
       <c r="T22" s="22"/>
       <c r="U22" s="22"/>
       <c r="V22" s="22"/>
@@ -2025,7 +2237,10 @@
       <c r="I23" s="22">
         <v>126.7</v>
       </c>
-      <c r="J23" s="22"/>
+      <c r="J23" s="22">
+        <f t="shared" si="0"/>
+        <v>117.10000000000001</v>
+      </c>
       <c r="K23" s="22"/>
       <c r="L23" s="22"/>
       <c r="M23" s="22"/>
@@ -2033,8 +2248,12 @@
       <c r="O23" s="22"/>
       <c r="P23" s="22"/>
       <c r="Q23" s="22"/>
-      <c r="R23" s="22"/>
-      <c r="S23" s="22"/>
+      <c r="R23" s="22">
+        <v>243.8</v>
+      </c>
+      <c r="S23" s="22">
+        <v>294.60000000000002</v>
+      </c>
       <c r="T23" s="22"/>
       <c r="U23" s="22"/>
       <c r="V23" s="22"/>
@@ -2068,23 +2287,41 @@
         <v>325.39999999999981</v>
       </c>
       <c r="H24" s="22">
-        <f t="shared" ref="H24:I24" si="6">+H22-H23</f>
+        <f t="shared" ref="H24:J24" si="13">+H22-H23</f>
         <v>0</v>
       </c>
       <c r="I24" s="22">
-        <f t="shared" si="6"/>
+        <f t="shared" si="13"/>
         <v>382.3</v>
       </c>
-      <c r="J24" s="22"/>
+      <c r="J24" s="22">
+        <f t="shared" si="13"/>
+        <v>360.9000000000002</v>
+      </c>
       <c r="K24" s="22"/>
       <c r="L24" s="22"/>
       <c r="M24" s="22"/>
       <c r="N24" s="22"/>
-      <c r="O24" s="22"/>
-      <c r="P24" s="22"/>
-      <c r="Q24" s="22"/>
-      <c r="R24" s="22"/>
-      <c r="S24" s="22"/>
+      <c r="O24" s="22">
+        <f t="shared" ref="O24:S24" si="14">+O22-O23</f>
+        <v>0</v>
+      </c>
+      <c r="P24" s="22">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="Q24" s="22">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="R24" s="22">
+        <f t="shared" ref="R24" si="15">+R22-R23</f>
+        <v>743.20000000000027</v>
+      </c>
+      <c r="S24" s="22">
+        <f>+S22-S23</f>
+        <v>898.00000000000011</v>
+      </c>
       <c r="T24" s="22"/>
       <c r="U24" s="22"/>
       <c r="V24" s="22"/>
@@ -2119,7 +2356,10 @@
       <c r="I25" s="22">
         <v>2.8</v>
       </c>
-      <c r="J25" s="22"/>
+      <c r="J25" s="22">
+        <f t="shared" si="0"/>
+        <v>4.3</v>
+      </c>
       <c r="K25" s="22"/>
       <c r="L25" s="22"/>
       <c r="M25" s="22"/>
@@ -2127,8 +2367,12 @@
       <c r="O25" s="22"/>
       <c r="P25" s="22"/>
       <c r="Q25" s="22"/>
-      <c r="R25" s="22"/>
-      <c r="S25" s="22"/>
+      <c r="R25" s="22">
+        <v>7.1</v>
+      </c>
+      <c r="S25" s="22">
+        <v>9.5</v>
+      </c>
       <c r="T25" s="22"/>
       <c r="U25" s="22"/>
       <c r="V25" s="22"/>
@@ -2151,19 +2395,19 @@
         <v>42</v>
       </c>
       <c r="C26" s="22">
-        <f t="shared" ref="C26:F26" si="7">+C24-C25</f>
+        <f t="shared" ref="C26:F26" si="16">+C24-C25</f>
         <v>0</v>
       </c>
       <c r="D26" s="22">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="E26" s="22">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>321.79999999999995</v>
       </c>
       <c r="F26" s="22">
-        <f t="shared" si="7"/>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="G26" s="22">
@@ -2171,23 +2415,50 @@
         <v>322.89999999999981</v>
       </c>
       <c r="H26" s="22">
-        <f t="shared" ref="H26:I26" si="8">+H24-H25</f>
+        <f t="shared" ref="H26:J26" si="17">+H24-H25</f>
         <v>0</v>
       </c>
       <c r="I26" s="22">
-        <f t="shared" si="8"/>
+        <f t="shared" si="17"/>
         <v>379.5</v>
       </c>
-      <c r="J26" s="22"/>
+      <c r="J26" s="22">
+        <f t="shared" si="17"/>
+        <v>356.60000000000019</v>
+      </c>
       <c r="K26" s="22"/>
-      <c r="L26" s="22"/>
-      <c r="M26" s="22"/>
-      <c r="N26" s="22"/>
-      <c r="O26" s="22"/>
-      <c r="P26" s="22"/>
-      <c r="Q26" s="22"/>
-      <c r="R26" s="22"/>
-      <c r="S26" s="22"/>
+      <c r="L26" s="22">
+        <f t="shared" ref="L26:T26" si="18">+L24-L25</f>
+        <v>0</v>
+      </c>
+      <c r="M26" s="22">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="N26" s="22">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="O26" s="22">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="P26" s="22">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="Q26" s="22">
+        <f t="shared" si="18"/>
+        <v>0</v>
+      </c>
+      <c r="R26" s="22">
+        <f t="shared" ref="R26:S26" si="19">+R24-R25</f>
+        <v>736.10000000000025</v>
+      </c>
+      <c r="S26" s="22">
+        <f t="shared" si="19"/>
+        <v>888.50000000000011</v>
+      </c>
       <c r="T26" s="22"/>
       <c r="U26" s="22"/>
       <c r="V26" s="22"/>
@@ -2245,11 +2516,11 @@
         <v>26</v>
       </c>
       <c r="C28" s="24" t="e">
-        <f t="shared" ref="C28:D28" si="9">+C26/C29</f>
+        <f t="shared" ref="C28:D28" si="20">+C26/C29</f>
         <v>#DIV/0!</v>
       </c>
       <c r="D28" s="24" t="e">
-        <f t="shared" si="9"/>
+        <f t="shared" si="20"/>
         <v>#DIV/0!</v>
       </c>
       <c r="E28" s="24">
@@ -2257,34 +2528,58 @@
         <v>2.6442070665571071</v>
       </c>
       <c r="F28" s="24" t="e">
-        <f t="shared" ref="F28:J28" si="10">+F26/F29</f>
+        <f t="shared" ref="F28:S28" si="21">+F26/F29</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G28" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="21"/>
         <v>2.6796680497925296</v>
       </c>
       <c r="H28" s="24" t="e">
-        <f t="shared" si="10"/>
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
       <c r="I28" s="24">
-        <f t="shared" si="10"/>
+        <f t="shared" si="21"/>
         <v>3.240819812126388</v>
       </c>
-      <c r="J28" s="24" t="e">
-        <f t="shared" si="10"/>
+      <c r="J28" s="24">
+        <f t="shared" si="21"/>
+        <v>3.0504704875962374</v>
+      </c>
+      <c r="K28" s="22"/>
+      <c r="L28" s="24" t="e">
+        <f t="shared" si="21"/>
         <v>#DIV/0!</v>
       </c>
-      <c r="K28" s="22"/>
-      <c r="L28" s="22"/>
-      <c r="M28" s="22"/>
-      <c r="N28" s="22"/>
-      <c r="O28" s="22"/>
-      <c r="P28" s="22"/>
-      <c r="Q28" s="22"/>
-      <c r="R28" s="22"/>
-      <c r="S28" s="22"/>
+      <c r="M28" s="24" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="N28" s="24" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="O28" s="24" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="P28" s="24" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="Q28" s="24" t="e">
+        <f t="shared" si="21"/>
+        <v>#DIV/0!</v>
+      </c>
+      <c r="R28" s="24">
+        <f t="shared" si="21"/>
+        <v>6.1495405179615723</v>
+      </c>
+      <c r="S28" s="24">
+        <f t="shared" si="21"/>
+        <v>7.6005132591958944</v>
+      </c>
       <c r="T28" s="22"/>
       <c r="U28" s="22"/>
       <c r="V28" s="22"/>
@@ -2319,7 +2614,9 @@
       <c r="I29" s="22">
         <v>117.1</v>
       </c>
-      <c r="J29" s="22"/>
+      <c r="J29" s="22">
+        <v>116.9</v>
+      </c>
       <c r="K29" s="22"/>
       <c r="L29" s="22"/>
       <c r="M29" s="22"/>
@@ -2327,8 +2624,12 @@
       <c r="O29" s="22"/>
       <c r="P29" s="22"/>
       <c r="Q29" s="22"/>
-      <c r="R29" s="22"/>
-      <c r="S29" s="22"/>
+      <c r="R29" s="22">
+        <v>119.7</v>
+      </c>
+      <c r="S29" s="22">
+        <v>116.9</v>
+      </c>
       <c r="T29" s="22"/>
       <c r="U29" s="22"/>
       <c r="V29" s="22"/>
